--- a/mocks/inventory/Inventory_Template_Mock_500.xlsx
+++ b/mocks/inventory/Inventory_Template_Mock_500.xlsx
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5012" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5012" uniqueCount="643">
   <si>
     <t>Category</t>
   </si>
@@ -1968,6 +1968,42 @@
   </si>
   <si>
     <t>NET-2026-000500</t>
+  </si>
+  <si>
+    <t>category_name</t>
+  </si>
+  <si>
+    <t>item_group</t>
+  </si>
+  <si>
+    <t>serial_number</t>
+  </si>
+  <si>
+    <t>cost</t>
+  </si>
+  <si>
+    <t>brand</t>
+  </si>
+  <si>
+    <t>descript_item</t>
+  </si>
+  <si>
+    <t>ownership</t>
+  </si>
+  <si>
+    <t>main_warehouse</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>sub_location</t>
+  </si>
+  <si>
+    <t>extra_serial_number</t>
+  </si>
+  <si>
+    <t>image_url</t>
   </si>
 </sst>
 </file>
@@ -2343,40 +2379,40 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>631</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>632</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>633</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>634</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>635</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>636</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>637</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>638</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
+        <v>639</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>9</v>
+        <v>640</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>10</v>
+        <v>641</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>11</v>
+        <v>642</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">

--- a/mocks/inventory/Inventory_Template_Mock_500.xlsx
+++ b/mocks/inventory/Inventory_Template_Mock_500.xlsx
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5012" uniqueCount="643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5012" uniqueCount="644">
   <si>
     <t>Category</t>
   </si>
@@ -2004,6 +2004,9 @@
   </si>
   <si>
     <t>image_url</t>
+  </si>
+  <si>
+    <t>device_name</t>
   </si>
 </sst>
 </file>
@@ -2382,7 +2385,7 @@
         <v>631</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>632</v>
+        <v>643</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>633</v>

--- a/mocks/inventory/Inventory_Template_Mock_500.xlsx
+++ b/mocks/inventory/Inventory_Template_Mock_500.xlsx
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5012" uniqueCount="644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5012" uniqueCount="646">
   <si>
     <t>Category</t>
   </si>
@@ -2007,6 +2007,12 @@
   </si>
   <si>
     <t>device_name</t>
+  </si>
+  <si>
+    <t>taxable_location</t>
+  </si>
+  <si>
+    <t>extra_info</t>
   </si>
 </sst>
 </file>
@@ -2403,7 +2409,7 @@
         <v>637</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>639</v>
@@ -2412,7 +2418,7 @@
         <v>640</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>642</v>
